--- a/RESULTS/tables/decision_curve_internal_cv.xlsx
+++ b/RESULTS/tables/decision_curve_internal_cv.xlsx
@@ -481,7 +481,7 @@
         <v>0.05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1893270266163715</v>
+        <v>0.1888601886289717</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>0.05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.18332859889148</v>
+        <v>0.1829344290813641</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>0.05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1864445222507757</v>
+        <v>0.1856892136202185</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>0.05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.185860974766526</v>
+        <v>0.1865304028239294</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         <v>0.05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1830929778318018</v>
+        <v>0.1829344290813641</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>0.05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1830026931266915</v>
+        <v>0.1824213477084201</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>0.05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1829982889947349</v>
+        <v>0.1826569687680982</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>0.05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1830004910607131</v>
+        <v>0.18253805720527</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         <v>0.1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1662413009218582</v>
+        <v>0.1695558995671962</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +624,7 @@
         <v>0.1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1535175190252384</v>
+        <v>0.1625873394418643</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         <v>0.1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1650790994333106</v>
+        <v>0.1680450376320842</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         <v>0.1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1625919882478185</v>
+        <v>0.1641772310781975</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         <v>0.1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1542241375302754</v>
+        <v>0.1625873394418643</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>0.1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1545774467827938</v>
+        <v>0.1613461082520954</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>0.1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1546425300661525</v>
+        <v>0.162089917204766</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>0.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.154605339618519</v>
+        <v>0.1616901198927055</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>0.15</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1487213185763825</v>
+        <v>0.1512218292613895</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         <v>0.15</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1299034989921662</v>
+        <v>0.1469788367210823</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>0.15</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1483103094381973</v>
+        <v>0.1502078426450284</v>
       </c>
     </row>
     <row r="27">
@@ -780,7 +780,7 @@
         <v>0.15</v>
       </c>
       <c r="C27" t="n">
-        <v>0.143488950745354</v>
+        <v>0.146877930285959</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         <v>0.15</v>
       </c>
       <c r="C28" t="n">
-        <v>0.13052370439829</v>
+        <v>0.1469788367210823</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         <v>0.15</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1299576439085738</v>
+        <v>0.1471880329890209</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>0.15</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1300560892111332</v>
+        <v>0.1474489130408031</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>0.15</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1299847163667777</v>
+        <v>0.1473307786777319</v>
       </c>
     </row>
     <row r="32">
@@ -871,7 +871,7 @@
         <v>0.2</v>
       </c>
       <c r="C34" t="n">
-        <v>0.133331241370654</v>
+        <v>0.1376093050499979</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>0.2</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1096502238400067</v>
+        <v>0.131856407681687</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.2</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1322643404041672</v>
+        <v>0.1369398769925944</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>0.2</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1263336262081085</v>
+        <v>0.1325362955524874</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>0.2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1106439061127149</v>
+        <v>0.131856407681687</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         <v>0.2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1097862014141668</v>
+        <v>0.1309987029831388</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>0.2</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1097652817873729</v>
+        <v>0.131260198318062</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         <v>0.2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1097339023471821</v>
+        <v>0.1311556001840927</v>
       </c>
     </row>
     <row r="42">
@@ -1001,7 +1001,7 @@
         <v>0.25</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1194371225750666</v>
+        <v>0.124541511512768</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         <v>0.25</v>
       </c>
       <c r="C45" t="n">
-        <v>0.09118167998549574</v>
+        <v>0.1157552682593476</v>
       </c>
     </row>
     <row r="46">
@@ -1027,7 +1027,7 @@
         <v>0.25</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1200228721252946</v>
+        <v>0.1249459576307825</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         <v>0.25</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1121013067793537</v>
+        <v>0.1208875500327741</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1053,7 @@
         <v>0.25</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0913908762534343</v>
+        <v>0.1157552682593476</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>0.25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.09086091237465657</v>
+        <v>0.1153229293056079</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1079,7 @@
         <v>0.25</v>
       </c>
       <c r="C50" t="n">
-        <v>0.09101432297114487</v>
+        <v>0.115643696916447</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         <v>0.25</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09097248371755716</v>
+        <v>0.1155600184092716</v>
       </c>
     </row>
     <row r="52">
@@ -1131,7 +1131,7 @@
         <v>0.3</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1085190697340817</v>
+        <v>0.1159545028002415</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         <v>0.3</v>
       </c>
       <c r="C55" t="n">
-        <v>0.07142558291045802</v>
+        <v>0.1037015785352675</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1157,7 @@
         <v>0.3</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1068395225543462</v>
+        <v>0.1138984023382166</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         <v>0.3</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1004321397191988</v>
+        <v>0.1092781533348873</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>0.3</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0735175455898438</v>
+        <v>0.1037015785352675</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         <v>0.3</v>
       </c>
       <c r="C59" t="n">
-        <v>0.07280030124262583</v>
+        <v>0.1033310022892049</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         <v>0.3</v>
       </c>
       <c r="C60" t="n">
-        <v>0.07283616345998672</v>
+        <v>0.103946637020567</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>0.3</v>
       </c>
       <c r="C61" t="n">
-        <v>0.07273455384413084</v>
+        <v>0.1034326119050608</v>
       </c>
     </row>
     <row r="62">
@@ -1261,7 +1261,7 @@
         <v>0.35</v>
       </c>
       <c r="C64" t="n">
-        <v>0.09662936536289116</v>
+        <v>0.1071438916298964</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>0.35</v>
       </c>
       <c r="C65" t="n">
-        <v>0.05077354343075443</v>
+        <v>0.09278980924518768</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>0.35</v>
       </c>
       <c r="C66" t="n">
-        <v>0.09518108350793175</v>
+        <v>0.1049939976763122</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         <v>0.35</v>
       </c>
       <c r="C67" t="n">
-        <v>0.09022474115984846</v>
+        <v>0.1020041002468516</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1313,7 @@
         <v>0.35</v>
       </c>
       <c r="C68" t="n">
-        <v>0.05229263017640073</v>
+        <v>0.09278980924518768</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         <v>0.35</v>
       </c>
       <c r="C69" t="n">
-        <v>0.05112113107594469</v>
+        <v>0.09186934566625794</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>0.35</v>
       </c>
       <c r="C70" t="n">
-        <v>0.05103423416464711</v>
+        <v>0.0922169333114482</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>0.35</v>
       </c>
       <c r="C71" t="n">
-        <v>0.05109860224708977</v>
+        <v>0.09212681799602848</v>
       </c>
     </row>
     <row r="72">
@@ -1391,7 +1391,7 @@
         <v>0.4</v>
       </c>
       <c r="C74" t="n">
-        <v>0.08928496715618595</v>
+        <v>0.1014601899502113</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>0.4</v>
       </c>
       <c r="C75" t="n">
-        <v>0.03294143899139507</v>
+        <v>0.08218624046413678</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>0.4</v>
       </c>
       <c r="C76" t="n">
-        <v>0.08623070164428268</v>
+        <v>0.09885220980991033</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>0.4</v>
       </c>
       <c r="C77" t="n">
-        <v>0.08165627658535905</v>
+        <v>0.09259026818961549</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>0.4</v>
       </c>
       <c r="C78" t="n">
-        <v>0.03549363346024574</v>
+        <v>0.08218624046413678</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>0.4</v>
       </c>
       <c r="C79" t="n">
-        <v>0.03506129450650601</v>
+        <v>0.08127972330306962</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         <v>0.4</v>
       </c>
       <c r="C80" t="n">
-        <v>0.03503340167078087</v>
+        <v>0.08179574076398478</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>0.4</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0351170801779563</v>
+        <v>0.08178179434612221</v>
       </c>
     </row>
     <row r="82">
@@ -1521,7 +1521,7 @@
         <v>0.45</v>
       </c>
       <c r="C84" t="n">
-        <v>0.08053675958784531</v>
+        <v>0.09472026655408103</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>0.45</v>
       </c>
       <c r="C85" t="n">
-        <v>0.02118207302090823</v>
+        <v>0.07219933741836593</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>0.45</v>
       </c>
       <c r="C86" t="n">
-        <v>0.08021345626466753</v>
+        <v>0.0907341267577241</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         <v>0.45</v>
       </c>
       <c r="C87" t="n">
-        <v>0.07336703295031399</v>
+        <v>0.08423763174610421</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         <v>0.45</v>
       </c>
       <c r="C88" t="n">
-        <v>0.02211775087386987</v>
+        <v>0.07219933741836593</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         <v>0.45</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0215396084606578</v>
+        <v>0.07076919565936762</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>0.45</v>
       </c>
       <c r="C90" t="n">
-        <v>0.02147494779602224</v>
+        <v>0.07148426653886678</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         <v>0.45</v>
       </c>
       <c r="C91" t="n">
-        <v>0.02142169783691059</v>
+        <v>0.07124083815435643</v>
       </c>
     </row>
     <row r="92">
@@ -1651,7 +1651,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C94" t="n">
-        <v>0.07049914229530146</v>
+        <v>0.08631438015145811</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>0.01263545458349024</v>
+        <v>0.06146186352035481</v>
       </c>
     </row>
     <row r="96">
@@ -1677,7 +1677,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C96" t="n">
-        <v>0.07401363959666959</v>
+        <v>0.08263252583573909</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>0.06623153842935443</v>
+        <v>0.07857411823773064</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>0.01255177607631481</v>
+        <v>0.06146186352035481</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>0.01271913309066567</v>
+        <v>0.06171289904188109</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>0.01267729383707795</v>
+        <v>0.06154554202753024</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>0.01271913309066567</v>
+        <v>0.06162922053470566</v>
       </c>
     </row>
     <row r="102">
@@ -1781,7 +1781,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>0.06271704112798628</v>
+        <v>0.07883910017711951</v>
       </c>
     </row>
     <row r="105">
@@ -1794,7 +1794,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C105" t="n">
-        <v>0.006596655648996561</v>
+        <v>0.05226652534296568</v>
       </c>
     </row>
     <row r="106">
@@ -1807,7 +1807,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0647532181359218</v>
+        <v>0.07644031630475713</v>
       </c>
     </row>
     <row r="107">
@@ -1820,7 +1820,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C107" t="n">
-        <v>0.05900264517058794</v>
+        <v>0.07039686856430927</v>
       </c>
     </row>
     <row r="108">
@@ -1833,7 +1833,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C108" t="n">
-        <v>0.005476293414036611</v>
+        <v>0.05226652534296568</v>
       </c>
     </row>
     <row r="109">
@@ -1846,7 +1846,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00540191251876956</v>
+        <v>0.05164823415105831</v>
       </c>
     </row>
     <row r="110">
@@ -1859,7 +1859,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00541121013067794</v>
+        <v>0.0520015434035768</v>
       </c>
     </row>
     <row r="111">
@@ -1872,7 +1872,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>0.005513483861670138</v>
+        <v>0.05172261504632536</v>
       </c>
     </row>
     <row r="112">
@@ -1911,7 +1911,7 @@
         <v>0.6</v>
       </c>
       <c r="C114" t="n">
-        <v>0.05432827078364923</v>
+        <v>0.0694322413288147</v>
       </c>
     </row>
     <row r="115">
@@ -1924,7 +1924,7 @@
         <v>0.6</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.002050123425798082</v>
+        <v>0.04336638634366764</v>
       </c>
     </row>
     <row r="116">
@@ -1937,7 +1937,7 @@
         <v>0.6</v>
       </c>
       <c r="C116" t="n">
-        <v>0.05455838667838167</v>
+        <v>0.06713108238149031</v>
       </c>
     </row>
     <row r="117">
@@ -1950,7 +1950,7 @@
         <v>0.6</v>
       </c>
       <c r="C117" t="n">
-        <v>0.05160871930044769</v>
+        <v>0.06468348604660894</v>
       </c>
     </row>
     <row r="118">
@@ -1963,7 +1963,7 @@
         <v>0.6</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.001045981339692897</v>
+        <v>0.04336638634366764</v>
       </c>
     </row>
     <row r="119">
@@ -1976,7 +1976,7 @@
         <v>0.6</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.001171499100456046</v>
+        <v>0.0424877620183256</v>
       </c>
     </row>
     <row r="120">
@@ -1989,7 +1989,7 @@
         <v>0.6</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.0011924187272499</v>
+        <v>0.04290615455420276</v>
       </c>
     </row>
     <row r="121">
@@ -2002,7 +2002,7 @@
         <v>0.6</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.001213338354043761</v>
+        <v>0.04280155642023347</v>
       </c>
     </row>
     <row r="122">
@@ -2041,7 +2041,7 @@
         <v>0.65</v>
       </c>
       <c r="C124" t="n">
-        <v>0.04752341503941854</v>
+        <v>0.060672894738415</v>
       </c>
     </row>
     <row r="125">
@@ -2054,7 +2054,7 @@
         <v>0.65</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.007399570848798918</v>
+        <v>0.03458313160836068</v>
       </c>
     </row>
     <row r="126">
@@ -2067,7 +2067,7 @@
         <v>0.65</v>
       </c>
       <c r="C126" t="n">
-        <v>0.04366822667312186</v>
+        <v>0.05676391304607697</v>
       </c>
     </row>
     <row r="127">
@@ -2080,7 +2080,7 @@
         <v>0.65</v>
       </c>
       <c r="C127" t="n">
-        <v>0.04312431637648156</v>
+        <v>0.05770828476991399</v>
       </c>
     </row>
     <row r="128">
@@ -2093,7 +2093,7 @@
         <v>0.65</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.00736370863143802</v>
+        <v>0.03458313160836068</v>
       </c>
     </row>
     <row r="129">
@@ -2106,7 +2106,7 @@
         <v>0.65</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.007327846414077121</v>
+        <v>0.03305898737052245</v>
       </c>
     </row>
     <row r="130">
@@ -2119,7 +2119,7 @@
         <v>0.65</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.007369685667664836</v>
+        <v>0.0331187577327906</v>
       </c>
     </row>
     <row r="131">
@@ -2132,7 +2132,7 @@
         <v>0.65</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.007327846414077121</v>
+        <v>0.03341163250790463</v>
       </c>
     </row>
     <row r="132">
@@ -2171,7 +2171,7 @@
         <v>0.7</v>
       </c>
       <c r="C134" t="n">
-        <v>0.03783663166115784</v>
+        <v>0.05273140593838473</v>
       </c>
     </row>
     <row r="135">
@@ -2184,7 +2184,7 @@
         <v>0.7</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.007726315495864885</v>
+        <v>0.02144959067263574</v>
       </c>
     </row>
     <row r="136">
@@ -2197,7 +2197,7 @@
         <v>0.7</v>
       </c>
       <c r="C136" t="n">
-        <v>0.03824107777917242</v>
+        <v>0.04826855222236168</v>
       </c>
     </row>
     <row r="137">
@@ -2210,7 +2210,7 @@
         <v>0.7</v>
       </c>
       <c r="C137" t="n">
-        <v>0.03655356121780122</v>
+        <v>0.04960740833716861</v>
       </c>
     </row>
     <row r="138">
@@ -2223,7 +2223,7 @@
         <v>0.7</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.008074975942429187</v>
+        <v>0.02144959067263574</v>
       </c>
     </row>
     <row r="139">
@@ -2236,7 +2236,7 @@
         <v>0.7</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.007698422660139741</v>
+        <v>0.01990153828989024</v>
       </c>
     </row>
     <row r="140">
@@ -2249,7 +2249,7 @@
         <v>0.7</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.007642636988689452</v>
+        <v>0.02118460873324687</v>
       </c>
     </row>
     <row r="141">
@@ -2262,7 +2262,7 @@
         <v>0.7</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.007642636988689452</v>
+        <v>0.02065464485446913</v>
       </c>
     </row>
     <row r="142">
@@ -2301,7 +2301,7 @@
         <v>0.75</v>
       </c>
       <c r="C144" t="n">
-        <v>0.03041713735826953</v>
+        <v>0.04464248357809297</v>
       </c>
     </row>
     <row r="145">
@@ -2314,7 +2314,7 @@
         <v>0.75</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.00711267310991172</v>
+        <v>0.007405547885025732</v>
       </c>
     </row>
     <row r="146">
@@ -2327,7 +2327,7 @@
         <v>0.75</v>
       </c>
       <c r="C146" t="n">
-        <v>0.02322078574118238</v>
+        <v>0.03510313376009372</v>
       </c>
     </row>
     <row r="147">
@@ -2340,7 +2340,7 @@
         <v>0.75</v>
       </c>
       <c r="C147" t="n">
-        <v>0.02556378394209447</v>
+        <v>0.04008200493703191</v>
       </c>
     </row>
     <row r="148">
@@ -2353,7 +2353,7 @@
         <v>0.75</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.008409689971130913</v>
+        <v>0.007405547885025732</v>
       </c>
     </row>
     <row r="149">
@@ -2366,7 +2366,7 @@
         <v>0.75</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.007782101167315176</v>
+        <v>0.005564620727166222</v>
       </c>
     </row>
     <row r="150">
@@ -2379,7 +2379,7 @@
         <v>0.75</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.007656583406552027</v>
+        <v>0.005857495502280239</v>
       </c>
     </row>
     <row r="151">
@@ -2392,7 +2392,7 @@
         <v>0.75</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.007656583406552027</v>
+        <v>0.005857495502280239</v>
       </c>
     </row>
     <row r="152">
@@ -2431,7 +2431,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C154" t="n">
-        <v>0.01962260993263881</v>
+        <v>0.03593991883184804</v>
       </c>
     </row>
     <row r="155">
@@ -2444,7 +2444,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.006150370277394247</v>
+        <v>-0.006275888038157391</v>
       </c>
     </row>
     <row r="156">
@@ -2457,7 +2457,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0010459813396929</v>
+        <v>0.02100330530103343</v>
       </c>
     </row>
     <row r="157">
@@ -2470,7 +2470,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C157" t="n">
-        <v>0.01426718547341117</v>
+        <v>0.02937115601857664</v>
       </c>
     </row>
     <row r="158">
@@ -2483,7 +2483,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.007489226392201159</v>
+        <v>-0.006275888038157391</v>
       </c>
     </row>
     <row r="159">
@@ -2496,7 +2496,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.007154512363499431</v>
+        <v>-0.007363708631438006</v>
       </c>
     </row>
     <row r="160">
@@ -2509,7 +2509,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.006819798334797704</v>
+        <v>-0.006526923559683685</v>
       </c>
     </row>
     <row r="161">
@@ -2522,7 +2522,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.006987155349148569</v>
+        <v>-0.006903476841973129</v>
       </c>
     </row>
     <row r="162">
@@ -2561,7 +2561,7 @@
         <v>0.85</v>
       </c>
       <c r="C164" t="n">
-        <v>0.008507314896168919</v>
+        <v>0.02068253769019427</v>
       </c>
     </row>
     <row r="165">
@@ -2574,7 +2574,7 @@
         <v>0.85</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.004825460580449911</v>
+        <v>-0.01550841666318006</v>
       </c>
     </row>
     <row r="166">
@@ -2600,7 +2600,7 @@
         <v>0.85</v>
       </c>
       <c r="C167" t="n">
-        <v>0.003096104765490985</v>
+        <v>0.01428113189127373</v>
       </c>
     </row>
     <row r="168">
@@ -2613,7 +2613,7 @@
         <v>0.85</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.004504692969610755</v>
+        <v>-0.01550841666318006</v>
       </c>
     </row>
     <row r="169">
@@ -2626,7 +2626,7 @@
         <v>0.85</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.004114193269458739</v>
+        <v>-0.01495055994867718</v>
       </c>
     </row>
     <row r="170">
@@ -2639,7 +2639,7 @@
         <v>0.85</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.004114193269458739</v>
+        <v>-0.01563393442394321</v>
       </c>
     </row>
     <row r="171">
@@ -2652,7 +2652,7 @@
         <v>0.85</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.004114193269458739</v>
+        <v>-0.01506213129157776</v>
       </c>
     </row>
     <row r="172">
@@ -2691,7 +2691,7 @@
         <v>0.9</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.000251035521526296</v>
+        <v>0.003012426258315552</v>
       </c>
     </row>
     <row r="175">
@@ -2704,7 +2704,7 @@
         <v>0.9</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.003514497301368145</v>
+        <v>-0.0193297351575248</v>
       </c>
     </row>
     <row r="176">
@@ -2730,7 +2730,7 @@
         <v>0.9</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.0086188862390695</v>
+        <v>0.00351449730136813</v>
       </c>
     </row>
     <row r="178">
@@ -2743,7 +2743,7 @@
         <v>0.9</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.0041839253587716</v>
+        <v>-0.0193297351575248</v>
       </c>
     </row>
     <row r="179">
@@ -2756,7 +2756,7 @@
         <v>0.9</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.004309443119534748</v>
+        <v>-0.01815823605706875</v>
       </c>
     </row>
     <row r="180">
@@ -2769,7 +2769,7 @@
         <v>0.9</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.004309443119534748</v>
+        <v>-0.01820007531065646</v>
       </c>
     </row>
     <row r="181">
@@ -2782,7 +2782,7 @@
         <v>0.9</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.004309443119534748</v>
+        <v>-0.01840927157859504</v>
       </c>
     </row>
     <row r="182">
@@ -2834,7 +2834,7 @@
         <v>0.95</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.003974729090833015</v>
+        <v>-0.01581523785615663</v>
       </c>
     </row>
     <row r="186">
@@ -2860,7 +2860,7 @@
         <v>0.95</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.02828333542529597</v>
+        <v>-0.01506213129157772</v>
       </c>
     </row>
     <row r="188">
@@ -2873,7 +2873,7 @@
         <v>0.95</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.003932889837245299</v>
+        <v>-0.01581523785615663</v>
       </c>
     </row>
     <row r="189">
@@ -2886,7 +2886,7 @@
         <v>0.95</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.003137944019078697</v>
+        <v>-0.01347223965524454</v>
       </c>
     </row>
     <row r="190">
@@ -2899,7 +2899,7 @@
         <v>0.95</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.003137944019078697</v>
+        <v>-0.01418350696623571</v>
       </c>
     </row>
     <row r="191">
@@ -2912,7 +2912,7 @@
         <v>0.95</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.003137944019078697</v>
+        <v>-0.01338856114806911</v>
       </c>
     </row>
   </sheetData>

--- a/RESULTS/tables/decision_curve_internal_cv.xlsx
+++ b/RESULTS/tables/decision_curve_internal_cv.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Net Benefit</t>
         </is>
